--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/198.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/198.xlsx
@@ -426,13 +426,13 @@
         <v>-1.788149337471403</v>
       </c>
       <c r="E2">
-        <v>-14.77101029424483</v>
+        <v>-15.77680248524445</v>
       </c>
       <c r="F2">
-        <v>-1.797371028656805</v>
+        <v>-3.000965670637208</v>
       </c>
       <c r="G2">
-        <v>-9.145048837805522</v>
+        <v>-8.627163646369633</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.857089049545736</v>
       </c>
       <c r="E3">
-        <v>-16.02148046435288</v>
+        <v>-16.23274736223273</v>
       </c>
       <c r="F3">
-        <v>-1.708367921430415</v>
+        <v>-3.241355405827417</v>
       </c>
       <c r="G3">
-        <v>-7.924215648742947</v>
+        <v>-9.137053870328181</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.973298243298674</v>
       </c>
       <c r="E4">
-        <v>-17.0366601819704</v>
+        <v>-16.335634291687</v>
       </c>
       <c r="F4">
-        <v>-1.975629066800036</v>
+        <v>-2.916906260070726</v>
       </c>
       <c r="G4">
-        <v>-9.167242735100796</v>
+        <v>-8.40674090327388</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.11940126095308</v>
       </c>
       <c r="E5">
-        <v>-16.42443766697741</v>
+        <v>-17.81973749279878</v>
       </c>
       <c r="F5">
-        <v>-2.002836794144986</v>
+        <v>-2.737153847132844</v>
       </c>
       <c r="G5">
-        <v>-8.852330401223163</v>
+        <v>-8.674180014118363</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.283383552117321</v>
       </c>
       <c r="E6">
-        <v>-16.43488938498712</v>
+        <v>-18.65320766238452</v>
       </c>
       <c r="F6">
-        <v>-2.392377393678856</v>
+        <v>-2.741154861688366</v>
       </c>
       <c r="G6">
-        <v>-8.539619580129147</v>
+        <v>-8.450867164766825</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.443784694203861</v>
       </c>
       <c r="E7">
-        <v>-17.51979401690074</v>
+        <v>-18.78046231047406</v>
       </c>
       <c r="F7">
-        <v>-1.987123492881282</v>
+        <v>-2.753855390708088</v>
       </c>
       <c r="G7">
-        <v>-8.646440953044809</v>
+        <v>-8.129509198724232</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.583545896413161</v>
       </c>
       <c r="E8">
-        <v>-20.40064162704233</v>
+        <v>-18.26571519849618</v>
       </c>
       <c r="F8">
-        <v>-1.885543283378187</v>
+        <v>-2.879525352651995</v>
       </c>
       <c r="G8">
-        <v>-8.273024658397176</v>
+        <v>-7.805976204262337</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.681463069351636</v>
       </c>
       <c r="E9">
-        <v>-20.21766863476241</v>
+        <v>-19.7363778887532</v>
       </c>
       <c r="F9">
-        <v>-2.242972220542535</v>
+        <v>-2.730055566858255</v>
       </c>
       <c r="G9">
-        <v>-7.858325860874833</v>
+        <v>-7.582564038544621</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.718606831023461</v>
       </c>
       <c r="E10">
-        <v>-20.41354777796419</v>
+        <v>-20.9780220630203</v>
       </c>
       <c r="F10">
-        <v>-1.760996587632476</v>
+        <v>-2.849081193864308</v>
       </c>
       <c r="G10">
-        <v>-7.825760024405022</v>
+        <v>-6.680228504178709</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.680865890632031</v>
       </c>
       <c r="E11">
-        <v>-21.21645074799816</v>
+        <v>-21.30607377708396</v>
       </c>
       <c r="F11">
-        <v>-1.829496773272175</v>
+        <v>-2.893464290938903</v>
       </c>
       <c r="G11">
-        <v>-6.708576705631488</v>
+        <v>-7.129098752757411</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.55888726956105</v>
       </c>
       <c r="E12">
-        <v>-20.21602479869763</v>
+        <v>-22.21162366744979</v>
       </c>
       <c r="F12">
-        <v>-2.557263925206098</v>
+        <v>-2.769429526248121</v>
       </c>
       <c r="G12">
-        <v>-5.676828635589927</v>
+        <v>-6.908278744196944</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.348792525218215</v>
       </c>
       <c r="E13">
-        <v>-23.05104878035561</v>
+        <v>-22.72155248308351</v>
       </c>
       <c r="F13">
-        <v>-1.782267405801562</v>
+        <v>-2.623397465175999</v>
       </c>
       <c r="G13">
-        <v>-5.380630815645794</v>
+        <v>-5.911764810329846</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.052241578502835</v>
       </c>
       <c r="E14">
-        <v>-21.13401440716252</v>
+        <v>-22.7105664051409</v>
       </c>
       <c r="F14">
-        <v>-1.933091572298879</v>
+        <v>-2.211549759852141</v>
       </c>
       <c r="G14">
-        <v>-4.995587885064241</v>
+        <v>-5.746773841743648</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.674468708067242</v>
       </c>
       <c r="E15">
-        <v>-24.85546906192595</v>
+        <v>-23.72952287008081</v>
       </c>
       <c r="F15">
-        <v>-1.734932835670792</v>
+        <v>-2.312225392151379</v>
       </c>
       <c r="G15">
-        <v>-4.86195771437156</v>
+        <v>-4.709046926458162</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.223214338125812</v>
       </c>
       <c r="E16">
-        <v>-23.36601773301111</v>
+        <v>-24.87823822923651</v>
       </c>
       <c r="F16">
-        <v>-1.267521558436755</v>
+        <v>-2.225758745912361</v>
       </c>
       <c r="G16">
-        <v>-4.839409588703584</v>
+        <v>-4.228716563619767</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.7083113390160926</v>
       </c>
       <c r="E17">
-        <v>-25.26854287548361</v>
+        <v>-25.1318599445101</v>
       </c>
       <c r="F17">
-        <v>-1.793444567167535</v>
+        <v>-2.421797690356684</v>
       </c>
       <c r="G17">
-        <v>-4.462580121604962</v>
+        <v>-4.13840157076291</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.1435447458122451</v>
       </c>
       <c r="E18">
-        <v>-26.60609560075917</v>
+        <v>-25.83976005833714</v>
       </c>
       <c r="F18">
-        <v>-0.9709353786406278</v>
+        <v>-2.388089764001966</v>
       </c>
       <c r="G18">
-        <v>-4.077557054296644</v>
+        <v>-4.248377893577499</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.4552010183127437</v>
       </c>
       <c r="E19">
-        <v>-27.04163517386889</v>
+        <v>-26.75049957991576</v>
       </c>
       <c r="F19">
-        <v>-1.60278421226959</v>
+        <v>-2.160145420671418</v>
       </c>
       <c r="G19">
-        <v>-3.822333856492071</v>
+        <v>-4.030557239275612</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.067755109215875</v>
       </c>
       <c r="E20">
-        <v>-26.19300820177948</v>
+        <v>-27.0224525579724</v>
       </c>
       <c r="F20">
-        <v>-0.7517203710007807</v>
+        <v>-1.754398641269178</v>
       </c>
       <c r="G20">
-        <v>-3.356434161659359</v>
+        <v>-3.253204730653805</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.6691494829849</v>
       </c>
       <c r="E21">
-        <v>-27.083029954773</v>
+        <v>-28.08614581763409</v>
       </c>
       <c r="F21">
-        <v>-0.5527150428870331</v>
+        <v>-1.817286637754911</v>
       </c>
       <c r="G21">
-        <v>-2.823899806212196</v>
+        <v>-3.209727336086556</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.230505423038538</v>
       </c>
       <c r="E22">
-        <v>-27.83818469487009</v>
+        <v>-28.16258645888356</v>
       </c>
       <c r="F22">
-        <v>-0.6384502407093791</v>
+        <v>-1.594166706178267</v>
       </c>
       <c r="G22">
-        <v>-3.496404027059745</v>
+        <v>-3.411667303436559</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.719340777250029</v>
       </c>
       <c r="E23">
-        <v>-28.01043878917385</v>
+        <v>-28.41713198285471</v>
       </c>
       <c r="F23">
-        <v>-0.6572392701396775</v>
+        <v>-1.677435025875076</v>
       </c>
       <c r="G23">
-        <v>-3.210955548481626</v>
+        <v>-3.186235704939888</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.10458895724074</v>
       </c>
       <c r="E24">
-        <v>-27.28139070173099</v>
+        <v>-28.33060190151615</v>
       </c>
       <c r="F24">
-        <v>-0.4238740905252092</v>
+        <v>-1.426559816100232</v>
       </c>
       <c r="G24">
-        <v>-2.437814053785772</v>
+        <v>-3.033232221751391</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.354884962139917</v>
       </c>
       <c r="E25">
-        <v>-28.33953658073328</v>
+        <v>-28.71336663854048</v>
       </c>
       <c r="F25">
-        <v>-0.6385844362286326</v>
+        <v>-1.317096862392096</v>
       </c>
       <c r="G25">
-        <v>-3.010045160794336</v>
+        <v>-2.873961875857054</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.44675038217752</v>
       </c>
       <c r="E26">
-        <v>-28.92990468016525</v>
+        <v>-29.45430197025348</v>
       </c>
       <c r="F26">
-        <v>-0.3881457760750637</v>
+        <v>-1.055662453333767</v>
       </c>
       <c r="G26">
-        <v>-1.961933064152157</v>
+        <v>-3.112599240509879</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.367664024150108</v>
       </c>
       <c r="E27">
-        <v>-29.39252905631485</v>
+        <v>-29.36947006666779</v>
       </c>
       <c r="F27">
-        <v>-0.535399679066315</v>
+        <v>-1.133406390821306</v>
       </c>
       <c r="G27">
-        <v>-1.901128274232363</v>
+        <v>-2.876322294826555</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.1117515154396</v>
       </c>
       <c r="E28">
-        <v>-28.0077488756133</v>
+        <v>-28.69393042809956</v>
       </c>
       <c r="F28">
-        <v>-0.6558724639250583</v>
+        <v>-1.503591357621363</v>
       </c>
       <c r="G28">
-        <v>-3.152054322246913</v>
+        <v>-3.129926635862424</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.688919548140601</v>
       </c>
       <c r="E29">
-        <v>-29.39613372162495</v>
+        <v>-28.4461142165038</v>
       </c>
       <c r="F29">
-        <v>-1.056456029305649</v>
+        <v>-1.345427027567839</v>
       </c>
       <c r="G29">
-        <v>-2.55728833175253</v>
+        <v>-3.082698393199181</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.119001375499225</v>
       </c>
       <c r="E30">
-        <v>-30.69122294613058</v>
+        <v>-28.18032902004562</v>
       </c>
       <c r="F30">
-        <v>-0.314353979466281</v>
+        <v>-1.004003805360384</v>
       </c>
       <c r="G30">
-        <v>-3.914466338849989</v>
+        <v>-3.611233609634905</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.428385267043903</v>
       </c>
       <c r="E31">
-        <v>-29.43652318129936</v>
+        <v>-28.43871016150126</v>
       </c>
       <c r="F31">
-        <v>-0.3617175424561483</v>
+        <v>-1.128848713371103</v>
       </c>
       <c r="G31">
-        <v>-2.605549464624025</v>
+        <v>-2.870191164487825</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.6539795075284821</v>
       </c>
       <c r="E32">
-        <v>-29.52936595540462</v>
+        <v>-28.11157772766116</v>
       </c>
       <c r="F32">
-        <v>-1.174132245812541</v>
+        <v>-1.421631858420977</v>
       </c>
       <c r="G32">
-        <v>-2.149078203487157</v>
+        <v>-4.016063670904682</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.1639813810758345</v>
       </c>
       <c r="E33">
-        <v>-28.22691343216252</v>
+        <v>-28.20193889801022</v>
       </c>
       <c r="F33">
-        <v>0.02791831932904399</v>
+        <v>-1.728456659315706</v>
       </c>
       <c r="G33">
-        <v>-2.023482726818287</v>
+        <v>-4.058627354903092</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.9831705799692186</v>
       </c>
       <c r="E34">
-        <v>-27.67333918404287</v>
+        <v>-26.52783451295861</v>
       </c>
       <c r="F34">
-        <v>-0.9990352576783927</v>
+        <v>-1.220259056270029</v>
       </c>
       <c r="G34">
-        <v>-3.333366280341717</v>
+        <v>-3.680569675409401</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.760871856507806</v>
       </c>
       <c r="E35">
-        <v>-27.68033114791072</v>
+        <v>-26.75640018154775</v>
       </c>
       <c r="F35">
-        <v>-0.006902104447633233</v>
+        <v>-1.345715299424014</v>
       </c>
       <c r="G35">
-        <v>-3.696728448186584</v>
+        <v>-3.927397329726382</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.460411533282266</v>
       </c>
       <c r="E36">
-        <v>-25.07991834764212</v>
+        <v>-26.89351784602601</v>
       </c>
       <c r="F36">
-        <v>-0.4213301742312119</v>
+        <v>-0.8963226699356708</v>
       </c>
       <c r="G36">
-        <v>-3.302300121001196</v>
+        <v>-4.671909226598618</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.051291438624513</v>
       </c>
       <c r="E37">
-        <v>-26.17641587301538</v>
+        <v>-25.50010186539183</v>
       </c>
       <c r="F37">
-        <v>0.06745878056687278</v>
+        <v>-1.23885673283028</v>
       </c>
       <c r="G37">
-        <v>-4.590165236142934</v>
+        <v>-4.848291782385448</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.512128279281843</v>
       </c>
       <c r="E38">
-        <v>-24.84762574494466</v>
+        <v>-26.18542300781663</v>
       </c>
       <c r="F38">
-        <v>0.2778417349580716</v>
+        <v>-1.064085293085432</v>
       </c>
       <c r="G38">
-        <v>-5.045520843433068</v>
+        <v>-4.90651434678461</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.831311803961044</v>
       </c>
       <c r="E39">
-        <v>-24.60202848561267</v>
+        <v>-24.52263527931019</v>
       </c>
       <c r="F39">
-        <v>-0.4889100436864012</v>
+        <v>-1.079453165142169</v>
       </c>
       <c r="G39">
-        <v>-4.898360473121386</v>
+        <v>-5.254389782596766</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.007648956820984</v>
       </c>
       <c r="E40">
-        <v>-25.45770176325801</v>
+        <v>-24.47300773266013</v>
       </c>
       <c r="F40">
-        <v>-0.4708160145070516</v>
+        <v>-0.9617868890441101</v>
       </c>
       <c r="G40">
-        <v>-4.589811007770233</v>
+        <v>-4.875749447088164</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.049372432157149</v>
       </c>
       <c r="E41">
-        <v>-21.558785269082</v>
+        <v>-23.44840426063265</v>
       </c>
       <c r="F41">
-        <v>-0.1515176572609681</v>
+        <v>-1.108063318500058</v>
       </c>
       <c r="G41">
-        <v>-5.66727440116359</v>
+        <v>-4.944019517199013</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.97268781927308</v>
       </c>
       <c r="E42">
-        <v>-22.26391848529036</v>
+        <v>-23.69761524222277</v>
       </c>
       <c r="F42">
-        <v>-0.5542574629910457</v>
+        <v>-1.12447741858653</v>
       </c>
       <c r="G42">
-        <v>-5.189539506027983</v>
+        <v>-4.935478309707694</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.800684632329757</v>
       </c>
       <c r="E43">
-        <v>-22.08823633616279</v>
+        <v>-22.78198496871587</v>
       </c>
       <c r="F43">
-        <v>-0.9106923592720338</v>
+        <v>-0.8459844396023505</v>
       </c>
       <c r="G43">
-        <v>-5.536206592718305</v>
+        <v>-5.255376325167469</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.5598724919824</v>
       </c>
       <c r="E44">
-        <v>-22.6613283072555</v>
+        <v>-21.75403495439672</v>
       </c>
       <c r="F44">
-        <v>-0.002052013304242128</v>
+        <v>-0.6707648530925878</v>
       </c>
       <c r="G44">
-        <v>-5.225021933117891</v>
+        <v>-5.62789215142842</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.28164963364013</v>
       </c>
       <c r="E45">
-        <v>-21.81975669767004</v>
+        <v>-21.31690588691031</v>
       </c>
       <c r="F45">
-        <v>0.6335277871069289</v>
+        <v>-0.7136552321073378</v>
       </c>
       <c r="G45">
-        <v>-4.133882676101805</v>
+        <v>-5.851201690234419</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.993873791434061</v>
       </c>
       <c r="E46">
-        <v>-21.54379149164261</v>
+        <v>-20.65999186193562</v>
       </c>
       <c r="F46">
-        <v>0.2820448711598763</v>
+        <v>-0.7090056058754242</v>
       </c>
       <c r="G46">
-        <v>-4.905484767121897</v>
+        <v>-5.125500313116321</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.724083389922887</v>
       </c>
       <c r="E47">
-        <v>-19.44499322872965</v>
+        <v>-19.61190825217837</v>
       </c>
       <c r="F47">
-        <v>0.4554992067342732</v>
+        <v>-0.402113707221069</v>
       </c>
       <c r="G47">
-        <v>-4.676212935799671</v>
+        <v>-5.971715479500507</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.498644685672605</v>
       </c>
       <c r="E48">
-        <v>-19.70351022440553</v>
+        <v>-19.79941877541398</v>
       </c>
       <c r="F48">
-        <v>0.3905411201089444</v>
+        <v>-0.5739121363572697</v>
       </c>
       <c r="G48">
-        <v>-6.35671868353559</v>
+        <v>-6.456832891188689</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.331631704771687</v>
       </c>
       <c r="E49">
-        <v>-19.10382705393978</v>
+        <v>-18.7931193953255</v>
       </c>
       <c r="F49">
-        <v>0.639724803647272</v>
+        <v>-0.6733601281655587</v>
       </c>
       <c r="G49">
-        <v>-4.988010046324849</v>
+        <v>-5.901204170059571</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.237630959684304</v>
       </c>
       <c r="E50">
-        <v>-15.69015919205569</v>
+        <v>-18.94256356605263</v>
       </c>
       <c r="F50">
-        <v>0.3926410314750411</v>
+        <v>-0.8112543078725784</v>
       </c>
       <c r="G50">
-        <v>-4.574661951382527</v>
+        <v>-6.461712635313575</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.223893319703313</v>
       </c>
       <c r="E51">
-        <v>-18.00664572899137</v>
+        <v>-17.54769394526199</v>
       </c>
       <c r="F51">
-        <v>0.1542252958057042</v>
+        <v>-0.7434615479948696</v>
       </c>
       <c r="G51">
-        <v>-5.991022581085537</v>
+        <v>-6.694079826715019</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.28326985913217</v>
       </c>
       <c r="E52">
-        <v>-15.69379102820984</v>
+        <v>-17.45543987277773</v>
       </c>
       <c r="F52">
-        <v>0.6670443605915998</v>
+        <v>-0.5464269059323821</v>
       </c>
       <c r="G52">
-        <v>-6.232973801823172</v>
+        <v>-6.421678208107169</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.414028219300094</v>
       </c>
       <c r="E53">
-        <v>-16.82959117949567</v>
+        <v>-15.51462648257037</v>
       </c>
       <c r="F53">
-        <v>0.294312992395337</v>
+        <v>-0.6731447526408308</v>
       </c>
       <c r="G53">
-        <v>-6.609167644178253</v>
+        <v>-5.620400386873049</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.604688863387866</v>
       </c>
       <c r="E54">
-        <v>-16.93856437801625</v>
+        <v>-16.04212124887984</v>
       </c>
       <c r="F54">
-        <v>0.9435857059747839</v>
+        <v>-0.6392206223939827</v>
       </c>
       <c r="G54">
-        <v>-6.516085035250565</v>
+        <v>-6.643100735955783</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.836032843212325</v>
       </c>
       <c r="E55">
-        <v>-14.46892937861516</v>
+        <v>-15.85867276682912</v>
       </c>
       <c r="F55">
-        <v>0.5093712524079362</v>
+        <v>-0.7476066984784784</v>
       </c>
       <c r="G55">
-        <v>-5.977535418558547</v>
+        <v>-7.395180539930793</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.098661843154744</v>
       </c>
       <c r="E56">
-        <v>-16.01592402674547</v>
+        <v>-14.92140997298758</v>
       </c>
       <c r="F56">
-        <v>0.2898232410721637</v>
+        <v>-0.8824756804304743</v>
       </c>
       <c r="G56">
-        <v>-7.597640262930462</v>
+        <v>-7.541387473127166</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.375931697187473</v>
       </c>
       <c r="E57">
-        <v>-15.62998030096776</v>
+        <v>-14.98734908301326</v>
       </c>
       <c r="F57">
-        <v>0.7772114265921144</v>
+        <v>-0.6638438434421979</v>
       </c>
       <c r="G57">
-        <v>-7.969659507360523</v>
+        <v>-7.180246681339151</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.65151296084505</v>
       </c>
       <c r="E58">
-        <v>-13.58601280133967</v>
+        <v>-14.84288623369457</v>
       </c>
       <c r="F58">
-        <v>0.1993207888467065</v>
+        <v>-0.5855051381594487</v>
       </c>
       <c r="G58">
-        <v>-7.054829974129401</v>
+        <v>-6.937418166033609</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.917878013772077</v>
       </c>
       <c r="E59">
-        <v>-13.92964699446372</v>
+        <v>-13.95305920508338</v>
       </c>
       <c r="F59">
-        <v>0.5206246235749675</v>
+        <v>-0.6066831791794208</v>
       </c>
       <c r="G59">
-        <v>-7.421244464961475</v>
+        <v>-7.584990668424907</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.161794284317107</v>
       </c>
       <c r="E60">
-        <v>-13.53043031136952</v>
+        <v>-12.77712771714158</v>
       </c>
       <c r="F60">
-        <v>0.5757102274937319</v>
+        <v>-0.3628772568200676</v>
       </c>
       <c r="G60">
-        <v>-7.851185014146624</v>
+        <v>-7.778422533738983</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.374955124974904</v>
       </c>
       <c r="E61">
-        <v>-12.43507848992021</v>
+        <v>-12.55344827200671</v>
       </c>
       <c r="F61">
-        <v>0.2259610845207386</v>
+        <v>-0.5829256020671311</v>
       </c>
       <c r="G61">
-        <v>-7.333971863455209</v>
+        <v>-8.407727445844582</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.553448040524638</v>
       </c>
       <c r="E62">
-        <v>-13.28976456023188</v>
+        <v>-11.69036188241081</v>
       </c>
       <c r="F62">
-        <v>0.4706823528601853</v>
+        <v>-0.5203515568270592</v>
       </c>
       <c r="G62">
-        <v>-7.105587258337507</v>
+        <v>-8.241283147766644</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.687654952628981</v>
       </c>
       <c r="E63">
-        <v>-12.81961386028154</v>
+        <v>-12.39217572717154</v>
       </c>
       <c r="F63">
-        <v>0.1270250237673796</v>
+        <v>-0.9434468347461291</v>
       </c>
       <c r="G63">
-        <v>-7.431613093590473</v>
+        <v>-7.637290666854313</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.77502556217414</v>
       </c>
       <c r="E64">
-        <v>-12.39676307134131</v>
+        <v>-11.31545404778979</v>
       </c>
       <c r="F64">
-        <v>0.4894465312683997</v>
+        <v>-0.6209203297313359</v>
       </c>
       <c r="G64">
-        <v>-7.288402204107141</v>
+        <v>-7.789747910028829</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.814128880233349</v>
       </c>
       <c r="E65">
-        <v>-11.9351304309994</v>
+        <v>-11.89207370013447</v>
       </c>
       <c r="F65">
-        <v>-0.4751450625540818</v>
+        <v>-0.8040566235096535</v>
       </c>
       <c r="G65">
-        <v>-8.128582245973236</v>
+        <v>-8.668244205966451</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.799361211679815</v>
       </c>
       <c r="E66">
-        <v>-12.11237943213362</v>
+        <v>-13.29286203645313</v>
       </c>
       <c r="F66">
-        <v>-0.5684051498634585</v>
+        <v>-1.013669196216249</v>
       </c>
       <c r="G66">
-        <v>-7.596143896346711</v>
+        <v>-7.958208330340184</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.734254165981355</v>
       </c>
       <c r="E67">
-        <v>-11.27430833295609</v>
+        <v>-10.66637881132238</v>
       </c>
       <c r="F67">
-        <v>-0.2452474288877322</v>
+        <v>-1.106835678009109</v>
       </c>
       <c r="G67">
-        <v>-7.770275281166836</v>
+        <v>-8.121520852337971</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.621079935436329</v>
       </c>
       <c r="E68">
-        <v>-11.9634107511773</v>
+        <v>-11.16057570825345</v>
       </c>
       <c r="F68">
-        <v>-0.0002246348136664182</v>
+        <v>-1.049176336569847</v>
       </c>
       <c r="G68">
-        <v>-7.557033111345762</v>
+        <v>-7.951620344717034</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.460835165330683</v>
       </c>
       <c r="E69">
-        <v>-11.72527188853594</v>
+        <v>-11.69837275293037</v>
       </c>
       <c r="F69">
-        <v>-0.4055754545973681</v>
+        <v>-0.7769598973966788</v>
       </c>
       <c r="G69">
-        <v>-6.988827627712952</v>
+        <v>-7.775836997672812</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.263570594980741</v>
       </c>
       <c r="E70">
-        <v>-11.39051803294093</v>
+        <v>-10.97660192321784</v>
       </c>
       <c r="F70">
-        <v>-0.07790727311339846</v>
+        <v>-1.2030588355183</v>
       </c>
       <c r="G70">
-        <v>-8.270614581244587</v>
+        <v>-8.376747360688082</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.034752952291353</v>
       </c>
       <c r="E71">
-        <v>-12.44551209403388</v>
+        <v>-11.6769575993481</v>
       </c>
       <c r="F71">
-        <v>-0.4427650091460519</v>
+        <v>-1.286766189938592</v>
       </c>
       <c r="G71">
-        <v>-9.265873818352302</v>
+        <v>-7.51039083524297</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.778131964339383</v>
       </c>
       <c r="E72">
-        <v>-12.20431651143735</v>
+        <v>-11.4906290078285</v>
       </c>
       <c r="F72">
-        <v>-0.4062646562764973</v>
+        <v>-1.543129333756984</v>
       </c>
       <c r="G72">
-        <v>-6.994448934038634</v>
+        <v>-7.44461691646873</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.50267767471967</v>
       </c>
       <c r="E73">
-        <v>-11.92162652150852</v>
+        <v>-11.34205430411084</v>
       </c>
       <c r="F73">
-        <v>-0.7116265603378819</v>
+        <v>-1.601209485836868</v>
       </c>
       <c r="G73">
-        <v>-6.40050395883799</v>
+        <v>-7.331065204471728</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.210198945014814</v>
       </c>
       <c r="E74">
-        <v>-11.82704934185833</v>
+        <v>-12.32566602942089</v>
       </c>
       <c r="F74">
-        <v>-0.6916173457232598</v>
+        <v>-1.823592998792423</v>
       </c>
       <c r="G74">
-        <v>-7.464023334419938</v>
+        <v>-6.739934192979465</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.902670607733373</v>
       </c>
       <c r="E75">
-        <v>-12.97696021815205</v>
+        <v>-12.13829588887952</v>
       </c>
       <c r="F75">
-        <v>-0.84531263363868</v>
+        <v>-1.82513376216163</v>
       </c>
       <c r="G75">
-        <v>-7.014388349821664</v>
+        <v>-6.752027615834423</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.583504363131925</v>
       </c>
       <c r="E76">
-        <v>-12.9381376104843</v>
+        <v>-12.47765520254033</v>
       </c>
       <c r="F76">
-        <v>-0.3034824856719402</v>
+        <v>-1.547817064889426</v>
       </c>
       <c r="G76">
-        <v>-6.745843516767065</v>
+        <v>-7.134024844519846</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.251093210064306</v>
       </c>
       <c r="E77">
-        <v>-13.66763401685392</v>
+        <v>-13.52307154110706</v>
       </c>
       <c r="F77">
-        <v>-0.8646425869830066</v>
+        <v>-2.055983189973797</v>
       </c>
       <c r="G77">
-        <v>-5.854849911418696</v>
+        <v>-7.0502945267406</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.906434809923423</v>
       </c>
       <c r="E78">
-        <v>-13.55935820333052</v>
+        <v>-13.53504029790933</v>
       </c>
       <c r="F78">
-        <v>-1.159747645862928</v>
+        <v>-1.929152685298567</v>
       </c>
       <c r="G78">
-        <v>-5.933349567245894</v>
+        <v>-5.753583633917929</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.550947432809325</v>
       </c>
       <c r="E79">
-        <v>-14.56413148767841</v>
+        <v>-14.6728148638625</v>
       </c>
       <c r="F79">
-        <v>-1.752241572552288</v>
+        <v>-2.06624003515526</v>
       </c>
       <c r="G79">
-        <v>-5.253542282938713</v>
+        <v>-6.222380056097504</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.185240858613521</v>
       </c>
       <c r="E80">
-        <v>-13.96241956085723</v>
+        <v>-14.57924753391602</v>
       </c>
       <c r="F80">
-        <v>-1.18184020449559</v>
+        <v>-2.15718400720641</v>
       </c>
       <c r="G80">
-        <v>-3.656780095164198</v>
+        <v>-6.301958949770505</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.8137181911409266</v>
       </c>
       <c r="E81">
-        <v>-15.61004142991198</v>
+        <v>-14.83319529931816</v>
       </c>
       <c r="F81">
-        <v>-1.471960976712867</v>
+        <v>-1.910725652423292</v>
       </c>
       <c r="G81">
-        <v>-5.852165058986347</v>
+        <v>-5.648324838496801</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.4410227273205793</v>
       </c>
       <c r="E82">
-        <v>-17.71602638107511</v>
+        <v>-15.54192412388861</v>
       </c>
       <c r="F82">
-        <v>-1.224569051866794</v>
+        <v>-1.985793134832386</v>
       </c>
       <c r="G82">
-        <v>-4.773910445209103</v>
+        <v>-5.131945945281282</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.07143759366671792</v>
       </c>
       <c r="E83">
-        <v>-16.53411730744319</v>
+        <v>-16.58304746909607</v>
       </c>
       <c r="F83">
-        <v>-1.567922370122773</v>
+        <v>-2.706036225646681</v>
       </c>
       <c r="G83">
-        <v>-4.509447514804425</v>
+        <v>-4.742741658956865</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.2875734669011856</v>
       </c>
       <c r="E84">
-        <v>-18.95344548909306</v>
+        <v>-18.06461019628955</v>
       </c>
       <c r="F84">
-        <v>-1.538241137713064</v>
+        <v>-2.461752335295912</v>
       </c>
       <c r="G84">
-        <v>-4.741801464023712</v>
+        <v>-4.565452013692275</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.6298158431842837</v>
       </c>
       <c r="E85">
-        <v>-18.75342279217426</v>
+        <v>-19.06681130740108</v>
       </c>
       <c r="F85">
-        <v>-1.810291903405672</v>
+        <v>-2.800505729364145</v>
       </c>
       <c r="G85">
-        <v>-3.725202450369855</v>
+        <v>-4.305663573589047</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.9495142160253377</v>
       </c>
       <c r="E86">
-        <v>-20.45993293722476</v>
+        <v>-19.79166149943884</v>
       </c>
       <c r="F86">
-        <v>-1.703811900715018</v>
+        <v>-2.944041919451632</v>
       </c>
       <c r="G86">
-        <v>-4.043888806162257</v>
+        <v>-4.424449258083636</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.238569332962162</v>
       </c>
       <c r="E87">
-        <v>-20.93065875337408</v>
+        <v>-20.28506591341857</v>
       </c>
       <c r="F87">
-        <v>-2.158437327086845</v>
+        <v>-3.504907950334704</v>
       </c>
       <c r="G87">
-        <v>-3.616139838124105</v>
+        <v>-4.1795979994536</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.490853172063026</v>
       </c>
       <c r="E88">
-        <v>-22.89125704652095</v>
+        <v>-21.57786825855032</v>
       </c>
       <c r="F88">
-        <v>-2.264759939970967</v>
+        <v>-3.000627696736866</v>
       </c>
       <c r="G88">
-        <v>-3.553361963062906</v>
+        <v>-3.263381347641524</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.699925507573419</v>
       </c>
       <c r="E89">
-        <v>-23.56687819762132</v>
+        <v>-23.01737957610858</v>
       </c>
       <c r="F89">
-        <v>-2.508997441747179</v>
+        <v>-3.48368186400537</v>
       </c>
       <c r="G89">
-        <v>-3.018189102820943</v>
+        <v>-4.051264701623753</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.858476087871963</v>
       </c>
       <c r="E90">
-        <v>-24.03472390430176</v>
+        <v>-25.49256648464307</v>
       </c>
       <c r="F90">
-        <v>-2.566403302761185</v>
+        <v>-3.637976889920417</v>
       </c>
       <c r="G90">
-        <v>-3.799875115553656</v>
+        <v>-3.152934927360359</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.960744586051796</v>
       </c>
       <c r="E91">
-        <v>-27.91589330884171</v>
+        <v>-26.00268549618511</v>
       </c>
       <c r="F91">
-        <v>-2.380691614727564</v>
+        <v>-3.880819420990314</v>
       </c>
       <c r="G91">
-        <v>-3.148167741783809</v>
+        <v>-3.782329224195518</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.000546597155192</v>
       </c>
       <c r="E92">
-        <v>-28.58230354381048</v>
+        <v>-27.87629180364463</v>
       </c>
       <c r="F92">
-        <v>-2.92192285306208</v>
+        <v>-4.053718750404836</v>
       </c>
       <c r="G92">
-        <v>-3.38727189335767</v>
+        <v>-3.610018639421992</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.972355716469697</v>
       </c>
       <c r="E93">
-        <v>-30.27194512318241</v>
+        <v>-29.52662170015597</v>
       </c>
       <c r="F93">
-        <v>-3.798294975221219</v>
+        <v>-4.115300411496354</v>
       </c>
       <c r="G93">
-        <v>-2.67620643806869</v>
+        <v>-3.878146343738644</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.87334174246222</v>
       </c>
       <c r="E94">
-        <v>-32.93276776671333</v>
+        <v>-31.19152875449801</v>
       </c>
       <c r="F94">
-        <v>-3.756583363020653</v>
+        <v>-4.418164787838298</v>
       </c>
       <c r="G94">
-        <v>-3.260441583202652</v>
+        <v>-3.320306178189293</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.702648483635239</v>
       </c>
       <c r="E95">
-        <v>-34.19047443828563</v>
+        <v>-33.59305097634972</v>
       </c>
       <c r="F95">
-        <v>-3.948897139254586</v>
+        <v>-4.488551994421575</v>
       </c>
       <c r="G95">
-        <v>-2.949084775234196</v>
+        <v>-4.017636180035836</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.456719652588641</v>
       </c>
       <c r="E96">
-        <v>-35.78297119324502</v>
+        <v>-36.25527744682302</v>
       </c>
       <c r="F96">
-        <v>-3.717497675486961</v>
+        <v>-4.662801562702659</v>
       </c>
       <c r="G96">
-        <v>-4.087309921455337</v>
+        <v>-4.796190416688398</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.145437076103816</v>
       </c>
       <c r="E97">
-        <v>-38.65368407855745</v>
+        <v>-37.39475019052906</v>
       </c>
       <c r="F97">
-        <v>-4.257357137402441</v>
+        <v>-5.075184393368725</v>
       </c>
       <c r="G97">
-        <v>-4.200202834890024</v>
+        <v>-4.911814530192983</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.761680517615158</v>
       </c>
       <c r="E98">
-        <v>-42.79597208709068</v>
+        <v>-39.32904484240238</v>
       </c>
       <c r="F98">
-        <v>-4.880613315962163</v>
+        <v>-5.125888762094084</v>
       </c>
       <c r="G98">
-        <v>-4.939143083619667</v>
+        <v>-5.262027211155865</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.3316530063715399</v>
       </c>
       <c r="E99">
-        <v>-42.98132932093564</v>
+        <v>-40.19267238464219</v>
       </c>
       <c r="F99">
-        <v>-4.978418655210701</v>
+        <v>-5.578425874243453</v>
       </c>
       <c r="G99">
-        <v>-4.766014794097941</v>
+        <v>-5.241260158988016</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.1658150447463216</v>
       </c>
       <c r="E100">
-        <v>-45.74669857964464</v>
+        <v>-43.72069100793097</v>
       </c>
       <c r="F100">
-        <v>-5.075911699948383</v>
+        <v>-5.981211240180685</v>
       </c>
       <c r="G100">
-        <v>-5.75039888910915</v>
+        <v>-6.320435104425178</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.6722864741690546</v>
       </c>
       <c r="E101">
-        <v>-47.94306055081585</v>
+        <v>-45.81950738473996</v>
       </c>
       <c r="F101">
-        <v>-4.68412705312033</v>
+        <v>-5.586784929705103</v>
       </c>
       <c r="G101">
-        <v>-5.351358971987558</v>
+        <v>-6.709791675844401</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.257913178027636</v>
       </c>
       <c r="E102">
-        <v>-48.8108395716022</v>
+        <v>-47.77995850248159</v>
       </c>
       <c r="F102">
-        <v>-5.194432022838728</v>
+        <v>-5.971142434399657</v>
       </c>
       <c r="G102">
-        <v>-5.80677085855186</v>
+        <v>-7.018274930284769</v>
       </c>
     </row>
   </sheetData>
